--- a/docs/변수검수표.xlsx
+++ b/docs/변수검수표.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0_읽는법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1_ID구조와매칭" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2_요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="A_쓰기로했는데_못쓰는것" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B_안쓰기로했는데_검토할것" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="C_쓰되_주의할것" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="D_손봐야하는것" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="0. 문서 안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. ID 체계 및 매칭 방법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. 검토 결과 요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="A. 연계 불가 변수" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="B. 추가 검토 변수" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="C. 주의가 필요한 변수" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="D. 처리가 필요한 변수" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,13 +33,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F2A3C"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -48,16 +49,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EDF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="00DDE4EE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -66,23 +62,28 @@
       <diagonal/>
     </border>
     <border>
+      <top style="thin">
+        <color rgb="00BFC8D6"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00C8D0DC"/>
+        <color rgb="00BFC8D6"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="hair">
+        <color rgb="00D8DEE8"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -450,15 +451,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>구분</t>
@@ -466,335 +467,386 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>용어</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>이 문서는</t>
+          <t>개요</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>변수 검수표</t>
+          <t>문서의 목적</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2021년과 2025년 두 번 조사한 설문 자료를 대시보드용으로 정리하면서, 그대로 쓰면 안 되거나 판단이 필요한 항목을 모은 목록입니다. 시트 A~D로 나뉘어 있고 각각 성격이 다릅니다.</t>
+          <t>경기학교교육실태조사 1주기(2021)와 2주기(2025) 자료를 패널 시계열 대시보드용으로 정제하는 과정에서, 그대로 사용할 수 없거나 판단이 필요한 변수를 응답주체별로 정리한 검토 자료이다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>시트 안내</t>
+          <t>개요</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>A. 쓰기로 했는데 못 쓰는 것</t>
+          <t>검토 기준</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>연구원이 '사용'으로 표시했지만, 실제 데이터를 열어보니 두 해를 비교할 수 없는 항목입니다.</t>
+          <t>연구원이 작성한 변수매칭표의 '사용' 표시분 223개 문항을 기준으로 하되, 실제 원자료(SPSS)를 대조하여 사용 가능 여부를 재확인하였다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>시트 안내</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>B. 안 쓰기로 했는데 검토할 것</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>'사용' 표시는 없지만, 과업지시서가 요구하는 화면을 채우려면 필요해 보이는 항목입니다.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>검토 규모</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>총 43건. 연계 불가 10건, 추가 검토 12건, 주의 필요 11건, 처리 필요 10건.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>시트 안내</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>C. 쓰되 주의할 것</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>사용은 하지만 숫자를 해석하거나 화면에 표시할 때 오해를 부를 수 있는 항목입니다.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>시트 구성</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1. ID 체계 및 매칭 방법</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>주기 간 식별자 체계의 차이와 두 주기 자료를 연결한 방법을 기술한다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>시트 안내</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>D. 손봐야 하는 것</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>점수를 뒤집거나 빈칸을 채우는 등, 계산 전에 데이터를 손질해야 하는 항목입니다.</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>시트 구성</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>A. 연계 불가 변수</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>'사용'으로 표시되었으나 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>용어</t>
+          <t>시트 구성</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>B. 추가 검토 변수</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>'사용' 표시는 없으나 과업지시서 요구사항 충족을 위해 검토가 필요한 변수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>시트 구성</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>C. 주의가 필요한 변수</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>사용은 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>시트 구성</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D. 처리가 필요한 변수</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>역채점·재코딩·결측 보정 등 집계 전 데이터 처리가 필요한 변수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>변수</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>설문지의 문항 하나가 데이터에서는 열(칼럼) 하나가 됩니다. 그 열의 이름이 변수명입니다. 예: STQ32 = '지금 다니는 학교에 얼마나 만족하나요'</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>설문 문항 하나가 데이터에서 하나의 열로 저장되며, 그 열의 이름을 변수명이라 한다. 예: STQ32는 '현재 다니는 학교에 어느 정도 만족하는지'를 묻는 문항이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>1주기 / 2주기</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>1주기는 2021년 조사, 2주기는 2025년 조사입니다. 같은 조사를 4년 간격으로 두 번 한 것입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 2021년 조사, 2주기는 2025년 조사를 가리킨다. 동일 조사를 4년 간격으로 두 차례 실시하였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>결측</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>응답이 비어 있는 것입니다. 답을 안 했거나, 애초에 그 사람에게 묻지 않은 문항이거나, 입력이 누락된 경우 모두 빈칸이 됩니다. 이 셋을 구분하는 게 이 검수의 핵심입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>응답이 비어 있는 상태를 말한다. 무응답, 해당 없음(애초에 묻지 않은 경우), 입력 누락이 모두 빈칸으로 저장되므로 이 셋을 구분하는 것이 검토의 핵심이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>리커트 척도</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>'전혀 그렇지 않다 ~ 매우 그렇다'처럼 정도를 고르는 선택형 문항입니다. 보통 5점이고, 이 조사에는 4점·6점도 섞여 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>'전혀 그렇지 않다 ~ 매우 그렇다'와 같이 정도를 선택하는 문항 형식이다. 본 조사에는 4점·5점·6점 척도가 혼재한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>역문항</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>다른 문항과 뜻이 반대인 문항입니다. 예를 들어 '친구 관계' 묶음에서 다른 문항은 점수가 높을수록 좋은데, '친구가 나에게 상처를 준 적이 있다'는 점수가 높을수록 나쁩니다. 그냥 평균 내면 서로 상쇄되어 버립니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>같은 묶음 내 다른 문항과 의미 방향이 반대인 문항이다. 예를 들어 '친구 관계' 묶음에서 다른 문항은 점수가 높을수록 관계가 양호하나, '친구가 나에게 상처를 준 적이 있다'는 점수가 높을수록 부정적이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>역채점 / 역코딩</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>역문항의 점수를 뒤집어서 방향을 맞추는 작업입니다. 5점 척도라면 1↔5, 2↔4로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>역문항의 점수 방향을 다른 문항과 일치시키는 처리이다. 5점 척도에서는 1↔5, 2↔4로 치환한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>다중응답</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>'해당하는 것을 모두 고르세요' 형식입니다. 고른 항목은 1, 안 고른 항목은 0이 되어야 하는데 이 조사에서는 안 고른 항목이 빈칸으로 저장된 경우가 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>'해당하는 항목을 모두 선택' 형식의 문항이다. 선택 항목은 1, 미선택 항목은 0으로 저장되어야 하나, 본 조사에서는 미선택이 결측으로 저장된 사례가 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>조건부 응답</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>앞 문항의 답에 따라 답할 사람이 정해지는 문항입니다. 예: '상담을 받은 적 있다'고 한 사람에게만 '얼마나 도움이 됐나'를 묻습니다. 이런 문항은 응답자 수가 해마다 달라져서 평균만 비교하면 오해가 생깁니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>응답 기저(분모)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>그 숫자가 '몇 명 중'에서 나온 값인지를 뜻합니다. 두 해의 분모가 다르면 평균을 나란히 놓을 수 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>환산100</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>4점·5점·6점 척도가 섞여 있어 그대로는 비교가 안 되므로, 모든 점수를 0~100점으로 바꾼 값입니다. 계산식은 (평균−최저점)÷(최고점−최저점)×100 입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>선행 문항의 응답에 따라 응답 대상자가 결정되는 문항이다. 예를 들어 '상담 경험이 있다'고 응답한 대상자에게만 '도움 정도'를 묻는다. 주기별로 응답 대상자 규모가 달라지므로 평균만으로는 비교가 어렵다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>응답 기저</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>산출된 수치의 분모, 즉 '몇 명을 대상으로 계산한 값인가'를 뜻한다. 주기 간 기저가 다르면 평균을 직접 비교할 수 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>환산 100점</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>척도 점수가 상이한 문항을 비교하기 위해 모든 값을 0~100점으로 변환한 값이다. 산식은 (평균 − 척도 최소값) ÷ (척도 최대값 − 척도 최소값) × 100 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>하위척도</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>한 묶음처럼 보이는 문항들이 사실 두 가지 다른 것을 재고 있는 경우입니다. 예: 학습동기 8문항 중 앞 4개는 '시켜서 한다'(외재적), 뒤 4개는 '재미있어서 한다'(내재적)입니다. 합치면 안 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>하나의 문항 묶음이 실제로는 둘 이상의 구인을 측정하는 경우를 말한다. 예를 들어 학습동기 8문항 중 1~4번은 외재적 동기, 5~8번은 내재적 동기를 측정하므로 단일 평균으로 합산해서는 안 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>연계 판정 ①②③④</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>연구원이 두 해 문항을 대조해 매긴 등급입니다. ①=그대로 비교 가능, ②=조건부 가능, ③=측정 방식이 바뀌어 비교 불가, ④=한 해에만 있음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>지표ID</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>두 해의 변수명이 서로 달라서(예: Q28 ↔ STQ32) 붙인 고정 이름표입니다. 예: ST_SAT_TOTAL_01. 앞으로 3주기가 추가돼도 이 이름은 바뀌지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>연구원이 주기 간 문항을 대조하여 부여한 등급이다. ① 연계 가능, ② 조건부 가능, ③ 측정 방식 변경으로 비교 불가, ④ 한 주기에만 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>지표 ID</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>주기 간 변수명이 상이하므로(예: Q28 ↔ STQ32) 문항 단위로 부여한 고정 식별자이다. 예: ST_SAT_TOTAL_01. 3주기 이후에도 동일하게 유지된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>시계열</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>같은 항목을 여러 해에 걸쳐 나란히 놓고 변화를 보는 것입니다. 이 대시보드의 핵심 기능입니다.</t>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>동일 항목을 복수 시점에 걸쳐 비교하여 변화를 관찰하는 것으로, 본 대시보드의 핵심 기능이다.</t>
         </is>
       </c>
     </row>
@@ -812,12 +864,12 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>구분</t>
@@ -837,289 +889,289 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>① ID가 왜 문제인가</t>
+          <t>1. 검토 배경</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>배경</t>
+          <t>검토 목적</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>두 해 조사를 이어 붙이려면 '같은 대상'을 알아볼 수 있어야 합니다. 그래서 학생·교사·학교마다 붙은 ID를 먼저 확인했습니다. 결론부터 말하면, 학교는 이어지고 사람은 이어지지 않습니다.</t>
+          <t>두 주기 자료를 연결하기 위해서는 동일 대상을 식별할 수 있어야 한다. 이에 학생·교사·학교에 부여된 식별자 체계를 확인하였다. 결론적으로 학교 단위 연결은 성립하나 개인 단위 연결은 성립하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>② 파일에 있는 ID</t>
+          <t>1. 검토 배경</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SCHID (학교 ID)</t>
+          <t>변수명 변경 여부</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4자리 숫자입니다. 예: 1001. 학생·학부모·교사·학교·학교DB 다섯 파일 모두에 들어 있어서, 이 값으로 파일끼리 연결합니다.</t>
+          <t>식별자 변수명이 주기 간 변경되었을 가능성을 검토하기 위해 10개 파일 전체를 확인하였다. 양 주기 모두 SCHID·STUID·TID로 동일하며, 별도의 연결용 변수는 존재하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>② 파일에 있는 ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>STUID (학생 ID)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>8자리 숫자입니다. 앞 4자리가 학교 ID, 뒤 4자리가 그 학교 안에서의 순번입니다. 예: 10011001 = 1001번 학교의 1001번 학생. 양 주기 모두 이 구조가 100% 지켜집니다.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. 식별자 구조</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SCHID (학교 식별자)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4자리 정수이다(예: 1001). 학생·학부모·교사·학교·학교DB 5개 파일에 모두 포함되어 파일 간 결합 키로 사용된다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>② 파일에 있는 ID</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TID (교사 ID)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1주기는 7자리(학교ID 4 + 순번 3), 2주기는 8자리(학교ID 4 + 순번 4)입니다. 예: 1001001 → 10011491. 자릿수 자체가 다릅니다.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2. 식별자 구조</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>STUID (학생 식별자)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8자리 정수로, 앞 4자리가 학교 식별자, 뒤 4자리가 학교 내 일련번호이다(예: 10011001 = 1001번 학교의 1001번 응답자). STUID ÷ 10000 = SCHID 관계가 양 주기 모두 100% 성립한다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>③ 주기 간 무엇이 달라졌나</t>
+          <t>2. 식별자 구조</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>학생 순번 채번 규칙</t>
+          <t>TID (교사 식별자)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1주기는 학교마다 1001번부터 차례로 매겼고 최대 1067번까지 갔습니다(학교당 평균 49.6명). 2주기는 1001~8809번까지 흩어져 있습니다. 즉 같은 사람에게 같은 번호를 다시 주려고 만든 번호가 아닙니다.</t>
+          <t>1주기는 7자리(학교 식별자 4 + 일련번호 3), 2주기는 8자리(학교 식별자 4 + 일련번호 4)로 자릿수 체계가 상이하다. 예: 1001001 → 10011491.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>③ 주기 간 무엇이 달라졌나</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>교사 순번 채번 규칙</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1주기 순번은 1~78, 2주기는 1001~3800입니다. 자릿수와 시작 번호가 모두 달라 두 해 TID가 겹칠 수 없습니다.</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>3. 주기 간 차이</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>학생 일련번호 부여 규칙</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 학교별로 1001번부터 순차 부여하여 최대 1067번까지 사용하였다(학교당 평균 49.6명). 2주기는 1001~8809번 범위에 분산되어 있다. 동일 응답자에게 동일 번호를 재부여하기 위한 체계가 아니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>④ 검증 결과</t>
+          <t>3. 주기 간 차이</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>교사 일련번호 부여 규칙</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1주기 일련번호는 1~78, 2주기는 1001~3800이다. 자릿수와 시작 번호가 모두 상이하여 주기 간 식별자가 중복될 수 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>4. 검증 결과</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>학생 개인 연결 — 불가</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>두 해에 모두 나오는 STUID가 8,884명·5,173명 중 40명뿐입니다(0.8%). 그 40명은 전부 한 학교(1001번교)에서 나왔는데, 그 학교만 2주기에도 1001번부터 번호를 매겨 우연히 겹친 것입니다. 진짜로 같은 사람을 추적했다면 공통 학교 기준 최대 4,991명이 겹쳐야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>④ 검증 결과</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>양 주기에 공통으로 존재하는 STUID는 40건(2주기 5,173명 대비 0.8%)에 불과하며, 전부 단일 학교(SCHID=1001)에서 발생하였다. 해당 학교만 2주기에도 1001번부터 부여하여 우연히 중복된 것으로, 동일인 추적이었다면 공통 학교 기준 최대 4,991명이 일치해야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>4. 검증 결과</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>교사 개인 연결 — 불가</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>두 해에 모두 나오는 TID가 0명입니다. 자릿수 체계가 달라 애초에 겹칠 수 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>④ 검증 결과</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>애초에 불가능한 이유</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1주기(2021) 중학생은 2주기(2025)에는 고등학생입니다. 두 조사 모두 중학교 대상이므로, 같은 학생이 두 번 응답하는 것 자체가 불가능합니다. 이 조사는 '같은 사람을 따라가는' 것이 아니라 '같은 학교의 그때그때 중학생'을 조사한 것입니다.</t>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>양 주기 공통 TID는 0건이다. 자릿수 체계가 상이하여 구조적으로 중복이 불가능하다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>④ 검증 결과</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>학교 연결 — 가능(확인됨)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>176개 학교가 두 해에 모두 나옵니다. 같은 학교가 맞는지 확인하려고 잘 안 바뀌는 속성 세 가지를 대조했습니다. 설립구분(공립/사립), 지역규모(중소도시/읍면), 남녀공학 구분이 176개교 전부 100% 일치했고, 학급 수도 거의 같았습니다(상관계수 0.939, 평균 차이 2.2학급). 학교 ID는 주기 간 안정적입니다.</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>4. 검증 결과</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>조사 설계상 근거</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1주기(2021) 중학생은 2주기(2025) 시점에 고등학생이므로, 양 주기 모두 중학교를 대상으로 하는 이상 동일인의 재응답은 성립할 수 없다. 본 조사는 동일 표본을 추적하는 패널이 아니라 동일 학교의 재학생을 반복 조사하는 반복 횡단 설계이다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>⑤ 그래서 어떻게 매칭했나</t>
+          <t>4. 검증 결과</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1) 문항 연결</t>
+          <t>학교 단위 연결 — 가능</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>사람을 잇는 대신 '문항'을 이었습니다. 두 해 변수명이 달라(Q28 ↔ STQ32) 연구원이 만든 변수매칭표를 기준으로, 문항 하나마다 고정 이름표(지표ID)를 붙였습니다. 이 이름표로 2021년 값과 2025년 값을 나란히 놓습니다.</t>
+          <t>176개 학교가 양 주기에 공통으로 존재한다. 동일 학교 여부를 확인하기 위해 시간에 따라 변동이 적은 속성을 대조한 결과, 설립구분(공립/사립)·지역규모(중소도시/읍면지역)·남녀공학 구분이 176개교 전부 일치하였다(각 100%). 학급 수의 상관계수는 0.939, 평균 절대차는 2.22학급이다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>⑤ 그래서 어떻게 매칭했나</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2) 문항 번호가 아니라 내용으로</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>문항이 중간에 삭제되면서 번호가 한 칸씩 밀린 곳이 많습니다. 예를 들어 교사 연수 문항은 1주기 3)자기계발이 2주기에서 빠지면서 이후 번호가 전부 밀렸습니다(Q27_4 → TRQ14_3). 번호를 믿으면 엉뚱한 문항끼리 붙습니다. 그래서 항목 내용으로 대조했습니다.</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>4. 검증 결과</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>주기 내 학생–학부모 연결 — 가능</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>학부모 파일의 STUID는 응답자 본인이 아닌 자녀의 학생 식별자이다. 이에 동일 주기 내에서 학생 응답과 학부모 응답을 개인 단위로 결합할 수 있다(1주기 5,424쌍, 학부모 대비 91.2% / 2주기 1,180쌍, 79.6%).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>⑤ 그래서 어떻게 매칭했나</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>3) 학교 정보 연결</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>지역규모별 비교 화면을 만들려면 응답자가 어느 지역 학교에 다니는지 알아야 합니다. 각 응답자의 SCHID로 그 해의 학교DB를 찾아 지역규모(중소도시/읍면지역)를 붙였습니다.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5. 매칭 방법</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>문항 단위 연결</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>개인 단위 연결이 불가하므로 문항 단위로 연결하였다. 주기 간 변수명이 상이하므로(Q28 ↔ STQ32) 연구원 변수매칭표를 기준으로 문항마다 고정 식별자(indicator_id)를 부여하고, 원변수명은 속성으로 관리한다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>⑤ 그래서 어떻게 매칭했나</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>4) 집계 단위</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>개인 연결이 안 되므로 두 해를 각각 별개 집단으로 보고 평균을 냈습니다. '2021년 학생 8,884명의 평균'과 '2025년 학생 5,173명의 평균'을 비교하는 방식입니다. 같은 사람의 변화가 아니라 집단 전체의 변화입니다.</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5. 매칭 방법</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>문항 번호가 아닌 내용 기준</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>문항 삭제로 인해 이후 번호가 이동한 사례가 다수 존재한다. 예를 들어 교사 연수 문항은 1주기 3)자기계발이 2주기에서 삭제되며 이후 번호가 순차 이동하였다(Q27_4 → TRQ14_3). 번호를 기준으로 대응시킬 경우 상이한 항목이 연결되므로 항목 내용을 기준으로 대조하였다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>⑥ 덤으로 확인된 것</t>
+          <t>5. 매칭 방법</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>학부모 ID는 자녀의 학생 ID</t>
+          <t>학교 속성 결합</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>학부모 파일의 STUID는 본인 번호가 아니라 자녀의 학생 ID입니다. 그래서 같은 해 안에서는 학생 응답과 학부모 응답을 짝지을 수 있습니다. 1주기 5,424쌍, 2주기 1,180쌍입니다.</t>
+          <t>지역규모별 비교 화면 구성을 위해 각 응답자의 SCHID로 해당 주기 학교DB를 조회하여 지역규모 변수(YM1_DB0_3 / YM2_DB0_3)를 결합하였다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>⑥ 덤으로 확인된 것</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>활용 가능성</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>같은 사건을 학생과 학부모가 각각 답한 문항이 있습니다(예: 가족과 함께 간 문화활동 횟수). 짝을 지을 수 있으므로 평균 비교뿐 아니라 '두 사람의 답이 얼마나 일치하는가'도 볼 수 있습니다. 다만 이건 각 해 안에서만 가능합니다.</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>5. 매칭 방법</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>집계 단위</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>개인 단위 연결이 불가하므로 각 주기를 독립 표본으로 간주하여 집계하였다. 따라서 산출된 변화는 동일 개인의 변화가 아니라 집단 수준의 변화로 해석해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>⑦ 주의</t>
+          <t>6. 유의 사항</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>응답 학교 수는 파일마다 다름</t>
+          <t>응답 학교 수의 파일 간 불일치</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>학교DB에는 1주기 179교, 2주기 177교가 있지만 실제로 응답이 들어온 학교는 다릅니다. 학생 179→139교, 학부모 179→125교, 교사 179→161교, 학교 설문 179→104교입니다. 지역규모로 나누면 읍면지역 쪽 학교 수가 더 적어지므로 표본이 작아지는 점에 주의해야 합니다.</t>
+          <t>학교DB에는 1주기 179교, 2주기 177교가 등재되어 있으나 실제 응답이 수집된 학교 수는 상이하다. 학생 179→139교, 학부모 179→125교, 교사 179→161교, 학교 설문 179→104교이다. 지역규모로 분할할 경우 읍면지역 표본이 특히 축소되므로 최소 표본 기준 설정이 필요하다.</t>
         </is>
       </c>
     </row>
@@ -1138,11 +1190,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>시트</t>
@@ -1150,32 +1202,36 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>건수</t>
+          <t>대상 건수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>이시트는</t>
+          <t>시트 설명</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1_ID구조와매칭</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
+          <t>1. ID 체계 및 매칭 방법</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>두 해 자료를 어떻게 이어 붙였는지, 학생·교사·학교 ID가 어떻게 다른지 설명합니다. 먼저 읽어보시면 나머지가 이해됩니다.</t>
+          <t>주기 간 식별자 체계의 차이와 두 주기 자료의 연결 방법. 다른 시트를 읽기 전 참조 권장.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A_쓰기로했는데_못쓰는것</t>
+          <t>A. 연계 불가 변수</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1183,14 +1239,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>연구원이 '사용'으로 표시했지만 실제로는 두 해를 비교할 수 없는 항목입니다. 학생 1건, 학부모 7건, 교사 2건.</t>
+          <t>'사용' 표시분 중 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수. 학생 1건, 학부모 7건, 교사 2건.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>B_안쓰기로했는데_검토할것</t>
+          <t>B. 추가 검토 변수</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1198,14 +1254,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'사용' 표시는 없지만 과업지시서가 요구하는 화면을 채우려면 필요해 보이는 항목입니다. 특히 학교용 설문 3건은 '학교안전' 대분류 전체에 해당합니다.</t>
+          <t>'사용' 미표시분 중 과업지시서 요구사항 충족을 위해 검토가 필요한 변수. 학교용 3건은 '학교안전' 대분류 전체에 해당.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C_쓰되_주의할것</t>
+          <t>C. 주의가 필요한 변수</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1213,14 +1269,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사용은 하지만 숫자 해석이나 화면 표시에 주의가 필요한 항목입니다.</t>
+          <t>사용 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D_손봐야하는것</t>
+          <t>D. 처리가 필요한 변수</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1228,7 +1284,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>점수 뒤집기, 빈칸 채우기 등 계산 전 손질이 필요한 항목입니다. 4건은 이미 처리했고 6건이 남았습니다.</t>
+          <t>집계 전 데이터 처리가 필요한 변수. 4건 처리 완료, 6건 결정 대기.</t>
         </is>
       </c>
     </row>
@@ -1246,17 +1302,17 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="86" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="88" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>응답주체</t>
@@ -1264,37 +1320,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>지표ID</t>
+          <t>지표 ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>변수</t>
+          <t>변수 대응</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>문항</t>
+          <t>문항 내용</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>무엇이문제</t>
+          <t>연계 불가 사유</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>쉬운설명</t>
+          <t>상세 설명</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>지금처리</t>
+          <t>현재 처리</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>필요한결정</t>
+          <t>필요한 결정</t>
         </is>
       </c>
     </row>
@@ -1316,27 +1372,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>수업 - 선생님이 학습 과정을 점검하고 개선할 기회를 주신다</t>
+          <t>수업 — 선생님이 학습 과정을 점검하고 개선할 기회를 제공한다</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>두 해가 서로 다른 것을 묻고 있음</t>
+          <t>측정 내용 변경 (연계 판정 ③)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>문항 자리는 이어져 있지만 실제로 재는 내용이 달라졌습니다. 겉모습이 비슷하다고 이어 붙이면 '변화'가 아니라 '다른 질문에 대한 다른 답'을 변화로 착각하게 됩니다.</t>
+          <t>문항 위치는 대응하나 실제로 측정하는 내용이 변경되었다. 형식적 유사성만으로 연결할 경우 서로 다른 질문에 대한 응답 차이를 시점 간 변화로 오인하게 된다.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>시계열에서 제외. 각 해의 응답 분포는 그대로 제공</t>
+          <t>시계열 집계에서 제외. 주기별 응답 분포는 제공</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>없음 — 연구원이 이미 '비교 불가'로 판정</t>
+          <t>없음 — 연구원이 비교 불가로 판정한 사항</t>
         </is>
       </c>
     </row>
@@ -1358,279 +1414,279 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>자녀와 나누는 대화 주제 - 학교생활</t>
+          <t>자녀와의 대화 주제 — 학교생활</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2025년 자료에 '해당한다'는 응답이 한 건도 없음</t>
+          <t>2주기 '해당' 응답 부재</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>'해당하는 주제를 모두 고르세요' 문항인데, 2025년 자료에는 고르지 않은 사람(0)과 빈칸만 있고 고른 사람(1)이 아예 없습니다. 같은 묶음의 다른 항목은 정상입니다. 빈칸 비율(75%)이 2021년에 이 항목을 고른 비율(79%)과 거의 같아서, 빈칸이 사실은 '골랐다'는 뜻일 가능성이 큽니다.</t>
+          <t>다중응답 문항임에도 2주기 자료에 미선택(0)과 결측만 존재하고 선택(1) 응답이 전무하다. 동일 묶음의 PRQ3_2_1~4는 정상 기록되어 있다. 결측률 75.1%가 1주기 선택률 78.6%와 근접하여 결측이 실질적으로 '해당'을 의미할 가능성이 있다.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>추측으로 채우지 않고 시계열에서 제외</t>
+          <t>임의 보정 없이 시계열에서 제외</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>연구원이 원자료를 확인해 빈칸의 의미를 알려주면 즉시 반영</t>
+          <t>연구원의 원자료 확인 후 결측의 의미 회신 — 확인 시 즉시 반영 가능</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>PR_TALK_07</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Q8_2_6 → PRQ3_2_6</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>자녀와 나누는 대화 주제 - 친구관계</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2025년 자료에 '해당한다'는 응답이 한 건도 없음</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 문제입니다. 빈칸 비율 65%, 2021년 선택률 78%입니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>자녀와의 대화 주제 — 친구관계</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2주기 '해당' 응답 부재</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>위와 동일한 사유이다. 결측률 64.8%, 1주기 선택률 77.8%이다.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>연구원 원자료 확인</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>PR_EDU_COST_01</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Q3_1 → PRQ2_1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>학교에 낸 돈 (체험활동비, 방과후 수강료 등)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>'돈을 안 썼다'를 두 해가 다르게 기록함</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2021년에는 지출이 없으면 0이라고 적었고(빈칸 0%), 2025년에는 그냥 비워뒀습니다(빈칸 48%). 이 상태로 평균을 내면 2021년은 '안 쓴 사람까지 포함한 평균', 2025년은 '쓴 사람만의 평균'이 됩니다. 분모가 달라서 2025년이 무조건 높게 나옵니다.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>학교에 납부한 금액 (체험활동비, 방과후학교 수강료 포함)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>미지출 기록 방식 상이</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입하여 결측이 0%이나, 2주기는 공란 처리하여 결측이 48.4%이다. 이 상태로 평균을 산출하면 1주기는 미지출자를 포함한 전체 평균, 2주기는 지출자 한정 평균이 되어 응답 기저가 일치하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸을 0(미지출)으로 볼지 연구원 확인. 확인되면 바로 복구 가능</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측을 0(미지출)으로 처리할지 연구원 확인</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>PR_EDU_COST_02</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Q3_2_1 → PRQ2_2</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>사교육비 - 국어·영어·수학 등 주요교과</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 기록 방식 차이</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>그대로 계산하면 47.3만원 → 80.2만원으로 70% 늘어난 것처럼 보입니다. 하지만 이건 실제 증가가 아니라 분모가 달라서 생긴 착시입니다.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>사교육비 — 국어·영어·수학 등 주요교과</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>미지출 기록 방식 상이</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>보정 없이 산출할 경우 47.3만원 → 80.2만원(+70%)으로 나타나나, 이는 실질 증가가 아니라 응답 기저 차이에 기인한 것이다. 1주기 0값 비율 18.3%, 2주기 결측률 15.7%이다.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸의 의미 확인</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측 처리 기준 확인</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>PR_EDU_COST_03</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Q3_2_2 → PRQ2_3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>사교육비 - 영어를 제외한 외국어</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 기록 방식 차이</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>그대로 계산하면 2.0만원 → 7.8만원(+301%)으로 보입니다. 외국어 사교육은 원래 받는 사람이 적어서(2021년 92%가 0원) 착시가 특히 큽니다.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>사교육비 — 영어를 제외한 외국어</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>미지출 기록 방식 상이</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>보정 없이 산출할 경우 2.0만원 → 7.8만원(+301%)으로 나타난다. 1주기 0값 비율이 91.8%로 미지출자 비중이 높아 기저 차이에 의한 왜곡이 특히 크다.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸의 의미 확인</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측 처리 기준 확인</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>PR_EDU_COST_04</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Q3_2_3 → PRQ2_4</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>사교육비 - 예체능</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 기록 방식 차이</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>그대로 계산하면 6.3만원 → 29.5만원(+368%)입니다. 네 항목 중 착시가 가장 큽니다.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>사교육비 — 예체능</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>미지출 기록 방식 상이</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>보정 없이 산출할 경우 6.3만원 → 29.5만원(+368%)으로 5개 항목 중 왜곡이 가장 크다. 1주기 0값 비율 75.2%, 2주기 결측률 62.0%이다.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸의 의미 확인</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측 처리 기준 확인</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>PR_EDU_COST_05</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Q3_2_4 → PRQ2_5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>사교육비 - 기타</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 기록 방식 차이</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>2021년은 86%가 0원으로 적었고 2025년은 79%가 빈칸입니다.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>사교육비 — 기타</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>미지출 기록 방식 상이</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1주기 0값 비율 85.5%, 2주기 결측률 79.0%이다.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸의 의미 확인</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측 처리 기준 확인</t>
         </is>
       </c>
     </row>
@@ -1652,69 +1708,69 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>교사효능감·사기 - 나는 책임감이 높다</t>
+          <t>교사효능감·사기 — 나는 책임감이 높다</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>두 해가 서로 다른 것을 묻고 있음</t>
+          <t>측정 내용 변경 (연계 판정 ③)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>'교사 사기' 묶음(8~10번) 안에 있는 문항인데 두 해의 측정 방식이 달라졌습니다. 이 묶음의 평균을 쓸 때는 8번을 빼고 나머지 2문항으로 계산하는 게 안전합니다.</t>
+          <t>'교사 사기' 하위척도(8~10번)에 속하는 문항이나 주기 간 측정 방식이 변경되었다. 해당 하위척도의 평균을 산출할 경우 본 문항을 제외하고 나머지 2문항으로 구성하는 것이 타당하다.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>시계열에서 제외 (묶음 평균에서도 제외)</t>
+          <t>시계열 및 하위척도 평균에서 제외</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>없음 — 연구원 판정</t>
+          <t>없음 — 연구원 판정 사항</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>교사</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>TR_TRAIN_03</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Q27_3 → (없음)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>교사 연수 - 자기계발</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2025년 설문에서 이 항목이 삭제됨</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>비교할 상대가 없습니다. 참고로 이 항목이 빠지면서 뒤 항목들의 번호가 한 칸씩 밀렸습니다. 번호로 짝을 맞추면 엉뚱한 항목끼리 붙으므로 내용으로 대조했습니다.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>시계열에서 제외. 2021년 단독 값만 보유</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2021년 단독 값을 화면에 노출할지</t>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Q27_3 → (해당 없음)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>교사 연수 — 자기계발</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2주기 문항 삭제 (연계 판정 ④)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>대응 문항이 존재하지 않는다. 본 항목 삭제로 인해 후속 항목의 번호가 순차 이동하였으므로, 번호 기준 대응 시 상이한 항목이 연결된다.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>시계열에서 제외. 1주기 단독 값 보유</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1주기 단독 값의 화면 노출 여부</t>
         </is>
       </c>
     </row>
@@ -1732,16 +1788,16 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="88" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>응답주체</t>
@@ -1749,27 +1805,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>변수</t>
+          <t>변수 대응</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>문항</t>
+          <t>문항 내용</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>왜검토대상</t>
+          <t>검토 필요성</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>걸림돌</t>
+          <t>제약 사항</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>추가확인</t>
+          <t>상세 설명</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1796,205 +1852,205 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>과업지시서가 정한 9개 대분류 중 첫 번째인 '학생성장'의 유일한 내용입니다. 이게 빠지면 그 탭이 통째로 빕니다.</t>
+          <t>과업지시서 &lt;표 4&gt;의 9개 대분류 중 첫 번째인 '학생성장'의 유일한 소분류에 해당한다. 제외 시 해당 대분류가 공란이 된다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>연구원이 계산해 둔 점수인데 변수매칭표의 '참고' 시트에 있어서 '사용' 표시가 붙어 있지 않습니다. 시트에는 '연계 검토 가치 있음'이라고만 적혀 있습니다.</t>
+          <t>연구원이 산출한 점수이나 변수매칭표의 참고 시트에 수록되어 '사용' 표시가 부여되지 않았다. 시트에는 '연계 검토 가치 있음'으로 기재되어 있다.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>사회적·자율적 역량은 구성 문항 수가 늘었습니다(16→20문항, 12→15문항). 100점 만점으로 환산한 점수는 비교할 수 있지만 엄밀히 같은 잣대는 아닙니다.</t>
+          <t>사회적 역량은 구성 문항이 16개에서 20개로, 자율적 역량은 12개에서 15개로 증가하였다. 100점 환산값은 비교 가능하나 엄밀히 동일한 척도는 아니다. 인지적 역량은 양 주기 모두 24문항으로 동일하다.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>포함 권장. 제외하면 표4의 첫 대분류가 사라집니다.</t>
+          <t>포함 권장</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CC_total / SC_total / AC_total</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>역량 원점수 (총점)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>위 환산점수의 원본입니다.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>사회적 역량은 만점이 80점에서 100점으로, 자율적 역량은 48점에서 60점으로 바뀌었습니다.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>만점이 다르면 총점끼리 비교하는 것은 의미가 없습니다. 인지적 역량만 양 해 모두 24점 만점으로 같습니다.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>환산점수만 사용. 총점은 제외 권장</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>위 환산점수의 산출 기반이 되는 원점수이다.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>사회적 역량 만점이 80점에서 100점으로, 자율적 역량이 48점에서 60점으로 변경되었다.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>만점이 상이한 총점 간 직접 비교는 성립하지 않는다. 인지적 역량만 양 주기 24점 만점으로 동일하다.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>환산점수만 사용, 원점수 총점은 제외 권장</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Q17_1~5 → STQ29_1~4</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>차별을 겪은 경험 (성적·경제수준·외모·가족형태 등)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>과업지시서 표4의 '학교생활·관계' 대분류 안에 '체벌·차별 경험'이 소분류로 명시돼 있습니다.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>두 해의 코딩 방향이 정반대입니다. 2021년은 1=예/2=아니오, 2025년은 1=없다/2=있다입니다. 그대로 비교하면 결과가 거꾸로 나옵니다.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>항목 수도 5개에서 4개로 줄었고, 2021년에는 체벌과 차별이 별개 문항이었는데 2025년에는 '학교 내 상호존중'으로 재구성됐습니다.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>점수를 뒤집고 공통 4항목만 대응시키면 사용 가능</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>차별 경험 (성적·경제수준·외모·가족형태 등)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>과업지시서 &lt;표 4&gt;의 '학교생활·관계' 대분류에 소분류 '체벌·차별 경험'으로 명시되어 있다.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>주기 간 코딩 방향이 반전되어 있다. 1주기는 1=예 / 2=아니오, 2주기는 1=없다 / 2=있다이다. 보정 없이 비교할 경우 결과가 역전된다.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>항목 수도 5개에서 4개로 축소되었으며, 1주기는 체벌(Q16)과 차별(Q17)이 별개 문항이나 2주기는 '학교 내 상호존중'으로 재구성되었다.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>역코딩 후 공통 4개 항목으로 대응 시 사용 가능</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Q16_1~5</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>체벌을 겪은 경험 (6점 빈도)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>위와 같은 소분류 소속입니다.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2025년에는 대응 문항이 5점 인권침해 문항으로 바뀌었습니다. 묻는 방식과 점수 폭이 모두 다릅니다.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>'전혀 없다 ~ 거의 매일' 6단계와 '그렇다/아니다' 계열은 같은 잣대로 볼 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>시계열 불가. 2021년 참고자료로만</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>체벌 경험 (6점 빈도 척도)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>위와 동일 소분류에 해당한다.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2주기 대응 문항이 5점 인권침해 문항으로 변경되어 측정 방식과 척도가 모두 상이하다.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>'전혀 없다 ~ 거의 매일'의 6점 빈도 척도와 인식 계열 문항은 동일 척도로 비교할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>시계열 불가. 1주기 참고 자료로 한정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>(없음) → STQ1</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(해당 없음) → STQ1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>성별</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>남녀별로 나눠 보는 기본 교차분석 축입니다.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2021년 학생 파일에는 성별 변수 자체가 없습니다.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>학교DB의 남녀공학 구분으로는 개인 성별을 알 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2025년 단독 분석에만 사용</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>성별 교차분석의 기본 축이다.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1주기 학생 파일에 성별 변수가 존재하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>학교DB의 남녀공학 구분으로는 개인 단위 성별을 확인할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2주기 단년도 분석에 한정 사용</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>(없음) → K_total / K_conversion</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(해당 없음) → K_total / K_conversion</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>국어 기초학력 점수</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2025년에 새로 산출된 점수입니다.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2021년에는 없습니다.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>향후 '경기기초학력 종단조사'를 대시보드에 추가할 때 연결 고리가 될 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2주기에 신규 산출된 학력 지표이다.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1주기에 대응 변수가 존재하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>향후 경기기초학력 종단조사를 대시보드에 추가할 경우 연계 지점이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>시계열 불가. 확장 단계에서 재검토</t>
         </is>
@@ -2013,27 +2069,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>가구소득 / 가정의 경제적 수준</t>
+          <t>월평균 가구소득 / 가정의 경제적 수준</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>표4의 '교육격차·가정배경' 대분류에 '가구소득'이 소분류로 명시돼 있습니다.</t>
+          <t>과업지시서 &lt;표 4&gt;의 '교육격차·가정배경' 대분류에 소분류 '가구소득'으로 명시되어 있다.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2021년은 월평균 소득을 만원 단위로 직접 적게 했고, 2025년은 '저소득층/중산층/고소득층' 3개 중 고르게 했습니다. 실제 금액과 본인이 느끼는 계층은 다른 것입니다.</t>
+          <t>1주기는 월평균 소득을 만원 단위 연속형으로 직접 기입하였으나, 2주기는 저소득층·중산층·고소득층 3점 척도로 변경되었다. 실제 소득액과 주관적 계층 인식은 상이한 구인이다.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>연구원 판정도 '비교 불가'입니다.</t>
+          <t>연구원 판정도 ③ 비교 불가이다.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2021년 금액을 3등분해 순위만 대조하는 정도. 금액 수준 비교는 불가</t>
+          <t>1주기를 3분위로 변환하여 순위 상관 정도만 참고. 수준 비교는 불가</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2101,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>(없음) → TRQ18_1~4</t>
+          <t>(해당 없음) → TRQ18_1~4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2055,59 +2111,59 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>표4의 '디지털 리터러시' 대분류는 학생·교사·학교 세 주체를 명시했는데 현재 학생만 채워져 있습니다.</t>
+          <t>과업지시서 &lt;표 4&gt;의 '디지털 리터러시' 대분류는 학생·교사·학교 3개 주체를 명시하고 있으나 현재 학생 축만 구성되어 있다.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2025년 신규 문항입니다.</t>
+          <t>2주기 신규 문항이다.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>AI 기반 플랫폼 활용 등 최근 정책과 맞닿은 내용이라 단년도로도 활용 가치가 있습니다.</t>
+          <t>AI 기반 교수학습 플랫폼 활용 등 최근 정책 의제와 직결되어 단년도 지표로도 활용 가치가 있다.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>시계열 불가. 2025년 단독 카드로 노출 검토</t>
+          <t>시계열 불가. 2주기 단년도 지표로 노출 검토</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>교사</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Q8 → TRQ7 / TRQ9 / TRQ7_1</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>현재 직위 → (직위 / 고용형태 / 보직 여부로 분리)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>교사 배경별로 나눠 보는 교차분석 축입니다.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2021년에는 한 문항에서 5개 중 골랐는데(기간제/진로교사/교사/부장·수석/교장·교감), 2025년에는 세 문항으로 쪼개졌습니다.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>2021년 답을 재분류하면 근사치는 맞출 수 있습니다. 예: 1~4번→교사, 5번→교감·교장.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>교차분석 축이 필요하면 재코딩 후 사용</t>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>현재 직위 → 직위·고용형태·보직 여부로 분리</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>교사 배경별 교차분석의 축이다.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 5개 선택지 단일 문항이나(기간제·진로교사·교사·부장/수석·교장/교감), 2주기는 3개 문항으로 분리되었다.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1주기 응답을 재분류하면 근사 대응이 가능하다. 예: 1~4 → 교사, 5 → 교감·교장.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>교차분석 축 필요 시 재코딩 후 사용</t>
         </is>
       </c>
     </row>
@@ -2124,99 +2180,99 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>학교폭력 및 비행 발생 빈도 (따돌림, 폭력, 절도 등 8개 항목)</t>
+          <t>학교폭력 및 비행 발생 빈도 (따돌림·폭력·절도 등 8개 항목)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>표4의 9개 대분류 중 하나인 '학교안전'의 소분류 '학교폭력 빈도'가 바로 이것입니다. 현재 이 대분류는 완전히 비어 있습니다.</t>
+          <t>과업지시서 &lt;표 4&gt;의 대분류 '학교안전' 중 소분류 '학교폭력 빈도'에 해당한다. 현재 해당 대분류는 전체가 공란이다.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>연구원의 변수매칭 대상이 학생·학부모·교사 세 종류뿐이라 학교용 설문은 아예 검토되지 않았습니다. 데이터가 없는 게 아니라 매칭이 안 된 것입니다.</t>
+          <t>연구원 변수매칭 대상이 학생·학부모·교사 3종으로 한정되어 학교용 설문은 검토되지 않았다. 자료 부재가 아니라 매칭 미실시이다.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>직접 대조해 보니 8개 항목이 순서까지 그대로 대응합니다. 2025년에 자해·도박·약물 3개가 새로 추가됐습니다.</t>
+          <t>직접 대조 결과 8개 항목이 순서까지 대응한다. 2주기에 자해·도박·약물 3개 항목이 추가되었다.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>연구원 승인 시 즉시 연계 가능. 단 건수를 학생 수로 나눠 발생률로 바꿔야 함</t>
+          <t>연구원 승인 시 연계 가능. 단 발생 건수를 학생 수 대비 발생률로 환산 필요</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Q12_1~8 → SCQ14_1~8</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>학교안전교육 실시 횟수 (폭력예방, 재난안전, 응급처치 등 8개 항목)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>표4 '학교안전'의 나머지 소분류 '안전교육'입니다.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>위와 같이 학교용 설문이 매칭 대상 밖입니다.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>8개 항목의 이름이 완전히 동일합니다. 2025년에 '회복적 생활교육' 1개가 추가됐을 뿐입니다.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>연계 난이도가 가장 낮음. 승인 시 바로 반영 가능</t>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>학교안전교육 실시 횟수 (폭력예방·재난안전·응급처치 등 8개 항목)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>위 대분류의 나머지 소분류 '안전교육'에 해당한다.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>학교용 설문이 변수매칭 대상 밖이다.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8개 항목명이 완전히 동일하며 2주기에 '회복적 생활교육' 1개 항목만 추가되었다.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>연계 난이도가 가장 낮음. 승인 시 즉시 반영 가능</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>(학교용 설문 전체)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2021년 135개 변수 / 2025년 150개 변수</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>위 두 건 외에도 학교 차원의 정보가 다수 있습니다.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>변수매칭 자체가 이뤄지지 않았습니다.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>학교 응답은 2021년 179교, 2025년 104교로 표본이 작습니다. 지역규모로 나누면 더 작아집니다.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1주기 135개 변수 / 2주기 150개 변수</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>위 2건 외에도 학교 차원의 정보가 다수 포함되어 있다.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>변수매칭이 실시되지 않았다.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>학교 응답은 1주기 179교, 2주기 104교로 표본이 작으며 지역규모 분할 시 더욱 축소된다.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>'학교안전' 우선 검토 후 필요 시 확대</t>
         </is>
@@ -2236,16 +2292,16 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>응답주체</t>
@@ -2253,7 +2309,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>대상 변수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2263,22 +2319,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>무슨일</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>왜중요</t>
+          <t>유의 사항</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>현재상태</t>
+          <t>현재 처리</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>조치</t>
+          <t>권고 조치</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2346,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Q9_친구_4, Q9_친구_5 (2021년)</t>
+          <t>Q9_친구_4, Q9_친구_5 (1주기)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2300,17 +2356,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>변수 설명이 잘못 적혀 있습니다. '친구와 함께한 활동'을 묻는 변수인데 설명에는 '가족_4)서점에 같이 감', '가족_5)기타'라고 되어 있습니다.</t>
+          <t>변수 설명이 잘못 기재되어 있다. 친구 동반 활동을 측정하는 변수이나 설명에는 '가족_4)서점에 같이 감', '가족_5)기타'로 표기되어 있다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>원자료 코드북만 보고 작업하면 가족 항목과 친구 항목을 헷갈릴 수 있습니다.</t>
+          <t>원자료 코드북만 참조하여 작업할 경우 가족 항목과 친구 항목을 혼동할 수 있다.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>변수매칭표는 올바르게 매핑되어 있어 산출물의 지표명은 정상입니다.</t>
+          <t>변수매칭표는 정상 매핑되어 있어 산출물의 지표명에는 영향이 없다.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2320,113 +2376,113 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Q10_1_1~3 → STQ7_1_1~3</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>선택지 의미 변경</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>같은 0이라는 값이 2021년에는 '아니오', 2025년에는 '해당없음'을 뜻합니다.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>'안 받는다'와 '답을 안 했다'가 섞여 있으면 참여율이 왜곡됩니다.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>0/1 그대로 집계 중</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>동일한 0 값이 1주기에는 '아니오', 2주기에는 '해당없음'을 의미한다.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>미참여와 무응답이 구분되지 않을 경우 참여율이 왜곡된다.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0/1 값을 그대로 집계</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>연구원에 두 값의 구분 여부 확인</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>역량 점수 (2025년)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CC/SC/AC 역량 점수 (2주기)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>산출값 결측</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2025년 학생 5,173명 중 484명(9.4%)의 역량 점수가 비어 있습니다.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>역량 지표를 쓰면 그 화면만 표본이 4,689명으로 줄어듭니다.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>결측 제외하고 계산</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>결측 사유를 연구원에 확인</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2주기 학생 5,173명 중 484명(9.4%)의 역량 점수가 결측이다.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>역량 지표 사용 시 해당 화면의 표본이 4,689명으로 축소된다.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>결측 제외 후 산출</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>연구원에 결측 사유 확인</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>표본 전체</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>표본 규모 차이</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2021년 8,884명에서 2025년 5,173명으로 줄었습니다(58% 수준).</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>표본이 줄면 값이 더 흔들립니다. 작은 변화를 큰 변화로 오해할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>가중치 변수가 없어 단순 평균으로 계산</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>그래프에 응답자 수(N) 함께 표시</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1주기 8,884명에서 2주기 5,173명으로 감소하였다(58% 수준).</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>표본 축소 시 추정치의 변동성이 커져 소폭 변화를 유의한 변화로 오인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>가중치 변수가 존재하지 않아 단순 집계</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>그래프에 응답자 수(N) 병기</t>
         </is>
       </c>
     </row>
@@ -2443,138 +2499,138 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>조건부 응답</t>
+          <t>조건부 응답 기저</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>진로 상담 등이 '얼마나 도움이 됐는지' 묻는 문항인데, 앞 문항에서 '경험이 있다'고 답한 사람만 응답합니다. 항목별로 51~89%가 빈칸입니다.</t>
+          <t>진로·진학 준비 활동의 도움 정도를 묻는 문항으로, 선행 문항에서 경험 있음으로 응답한 대상자만 답변한다. 항목별 결측률은 51~89%이다.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>현재 헤드라인 카드 1위 지표입니다(+20.7%). 그런데 9개 항목이 모두 +12~13점씩 똑같이 올랐고, 문항 이름도 '만족도'에서 '인식'으로 바뀌었습니다. 응답한 사람 자체가 다른 집단일 수 있습니다.</t>
+          <t>현재 헤드라인 카드 1순위 지표이다(+20.7%). 9개 항목이 일제히 +12~13점 이동하였고 문항명이 '진학·진로 만족도'에서 '진로·진학 인식'으로 변경되었다. 응답 집단 자체가 상이할 가능성이 있다.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>집계에는 포함, 조건부 기저임을 표시</t>
+          <t>집계에 포함하되 조건부 기저임을 지표 정의에 표기</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>대표 지표로 전면 배치하기 전 검토 권장</t>
+          <t>대표 지표 배치 전 연구원 검토</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Q12_1~3 → PRQ12_1~3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>조건부 응답</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>공개수업 만족도인데 참여한 학부모만 답합니다. 빈칸이 2021년 81%, 2025년 59%입니다.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>빈칸 비율이 크게 달라졌다는 건 참여율 자체가 변했다는 뜻입니다. 만족도만 비교하면 '참여자가 늘었다'는 더 중요한 변화를 놓칩니다.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>조건부 응답 기저</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>공개수업 만족도로 참여자만 응답한다. 결측률이 1주기 81%, 2주기 59%이다.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>결측률 차이는 참여율 자체의 변화를 의미한다. 만족도만 비교할 경우 참여율 변화라는 더 중요한 정보를 누락하게 된다.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>만족도만 집계</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>참여율과 만족도를 나란히 제시</t>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>참여율과 만족도를 병렬 제시</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>교육비 6개 변수</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>교육비 관련 6개 변수</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>극단값</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>상위 1%를 넘는 극단적으로 큰 값이 있습니다. 예: 외국어 사교육비 상위 1%가 50만원인데 최대값이 500만원입니다(10배).</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>한 사람의 값이 평균을 크게 끌어올립니다.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>평균과 함께 중앙값·절사평균(상하위 1% 제외)을 같이 제공</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>화면에는 중앙값 사용 권장</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>상위 1% 값의 3배를 초과하는 극단값이 6건 확인되었다. 예: 외국어 사교육비 상위 1%가 50만원인 반면 최대값은 500만원이다.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>소수 응답이 평균을 크게 상향시킨다.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>평균과 함께 중앙값 및 절사평균(상하위 1% 제외)을 병기</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>화면 표시에는 중앙값 사용 권장</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>표본 전체</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>표본 규모 차이</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2021년 5,948명에서 2025년 1,482명으로 줄었습니다(25% 수준).</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>세 응답주체 중 감소폭이 가장 큽니다. 학부모 지표는 특히 조심해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>가중치 없음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>그래프에 N 표시 필수</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1주기 5,948명에서 2주기 1,482명으로 감소하였다(25% 수준).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3개 응답주체 중 감소폭이 가장 크므로 학부모 지표 해석에 특히 유의해야 한다.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>가중치 미적용</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>그래프에 응답자 수(N) 병기 필수</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2652,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2021년 5,189명에서 2025년 2,800명으로 줄었습니다(54% 수준).</t>
+          <t>1주기 5,189명에서 2주기 2,800명으로 감소하였다(54% 수준).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>위와 같습니다.</t>
+          <t>위와 동일하다.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>가중치 없음</t>
+          <t>가중치 미적용</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>그래프에 N 표시</t>
+          <t>그래프에 응답자 수(N) 병기</t>
         </is>
       </c>
     </row>
@@ -2623,69 +2679,69 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SCHID (학교 수)</t>
+          <t>SCHID (응답 학교 수)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>응답 학교 수 불일치</t>
+          <t>파일 간 학교 수 불일치</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>학교DB에는 179→177교가 있지만 실제 응답이 들어온 학교는 학생 179→139교, 학부모 179→125교, 교사 179→161교, 학교설문 179→104교로 제각각입니다.</t>
+          <t>학교DB에는 179→177교가 등재되어 있으나 실제 응답 학교는 학생 179→139교, 학부모 179→125교, 교사 179→161교, 학교 설문 179→104교이다.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>지역규모(중소도시/읍면)로 나누면 읍면지역 학교 수가 특히 적어집니다. 표본이 너무 작은 칸이 생길 수 있습니다.</t>
+          <t>지역규모로 분할 시 읍면지역 표본이 특히 축소되어 표본이 과소한 셀이 발생할 수 있다.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>학교 목록은 학교DB 기준이라 응답이 없는 학교도 포함되어 있음</t>
+          <t>dim_school은 학교DB 기준이므로 응답이 없는 학교도 포함</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>응답 유무 표시 추가 + 최소 표본 기준 설정</t>
+          <t>응답 유무 플래그 추가 및 최소 표본 기준 설정</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>응답주체 간 비교 27개 조합</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>다계열 그래프 불가</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>같은 주제를 여러 주체가 답한 경우 한 화면에 여러 선으로 그리게 되어 있는데, 27개 조합 중 15개가 성립하지 않습니다. 한쪽 주체의 문항이 '사용'으로 선택되지 않았기 때문입니다.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>업체가 여러 선이 그려질 것으로 보고 화면을 만들면 빈 선이 나옵니다. 특히 디지털 리터러시 교육, 학생중심수업, 학부모회 활성화가 여기 해당합니다.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>산출물에 이 정보가 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>'깨진 조합' 목록을 산출물에 추가 예정</t>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>다계열 구성 불가</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>동일 주제에 대한 복수 주체 응답을 하나의 화면에 다계열로 제시하는 구조이나, 27개 조합 중 15개는 한쪽 주체 문항이 '사용' 미선택되어 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>업체가 다계열을 전제로 화면을 설계할 경우 빈 계열이 발생한다. 디지털 리터러시 교육, 학생중심수업, 학부모회 활성화가 이에 해당한다.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>산출물에 해당 정보가 포함되어 있지 않음</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>성립 불가 조합 목록을 산출물에 추가</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2759,16 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>응답주체</t>
@@ -2720,32 +2776,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>변수</t>
+          <t>대상 변수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>조치</t>
+          <t>처리 방법</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>문항</t>
+          <t>문항 내용</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>왜필요</t>
+          <t>필요한 이유</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>현재상태</t>
+          <t>현재 상태</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>결정</t>
+          <t>결정 사항</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2818,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>점수 뒤집기(역채점)</t>
+          <t>역채점</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2772,54 +2828,54 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>같은 묶음의 다른 문항은 점수가 높을수록 관계가 좋다는 뜻인데 이 문항만 반대입니다. 그냥 평균 내면 서로 상쇄됩니다.</t>
+          <t>동일 묶음의 다른 문항은 점수가 높을수록 관계가 양호함을 의미하나 본 문항은 반대이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>뒤집지 않고 표시만 함. 묶음 평균 계산에서는 제외 중</t>
+          <t>역채점하지 않고 표기만 함. 하위척도 평균 산출에서 제외</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>뒤집을지 연구원 확인</t>
+          <t>역채점 여부 연구원 확인</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Q17_1~5 → STQ29_1~4</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>점수 뒤집기(역코딩)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>차별을 겪은 경험</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2021년은 1=예/2=아니오, 2025년은 1=없다/2=있다로 방향이 정반대입니다. 손대지 않으면 결과가 거꾸로 나옵니다.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>현재 사용하지 않는 문항</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>사용하기로 하면 뒤집기는 필수</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>역코딩</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>차별 경험</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 1=예 / 2=아니오, 2주기는 1=없다 / 2=있다로 코딩 방향이 반전되어 있다. 보정하지 않으면 결과가 역전된다.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>현재 미사용 변수</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>사용 결정 시 역코딩 필수</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2892,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>점수 뒤집기(역채점)</t>
+          <t>역채점</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2846,128 +2902,128 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>위 학생 문항과 같은 이유입니다.</t>
+          <t>위 학생 문항과 동일한 사유이다.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>표시만 함. 묶음 평균에서 제외</t>
+          <t>표기만 함. 하위척도 평균에서 제외</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>뒤집을지 연구원 확인</t>
+          <t>역채점 여부 연구원 확인</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Q13_5 → PRQ13_5</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>점수 뒤집기(역채점)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>역채점</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>학교 선생님들은 내 아이에게 관심이 부족하다</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>위와 같습니다.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>표시만 함. 묶음 평균에서 제외</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>뒤집을지 연구원 확인</t>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>위와 동일하다.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>표기만 함. 하위척도 평균에서 제외</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>역채점 여부 연구원 확인</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Q8_2_1~6</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>빈칸을 0으로 채우기</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>자녀와 나누는 대화 주제 (다중응답)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>'고른 것을 모두 표시'하는 문항인데 2021년 자료에는 고른 사람(1)만 있고 안 고른 사람은 빈칸입니다. 빈칸을 그냥 두면 '고른 사람만 세기'가 되어 선택률이 항상 100%로 나옵니다.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>적용 완료 (2026-09-07). 이전에는 다른 규칙과 충돌해 보정이 취소되고 있었습니다</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>결측 보정 (결측 → 0)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>자녀와의 대화 주제 (다중응답)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>다중응답 문항이나 1주기 자료에 선택(1)만 기록되고 미선택은 결측으로 저장되어 있다. 보정하지 않으면 선택자만 집계되어 선택률이 항상 100%로 산출된다.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>적용 완료(2026-09-07). 이전에는 후속 규칙과 충돌하여 보정이 무효화되고 있었음</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>PRQ2_1~5</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>빈칸 처리 기준 통일</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>교육비·사교육비</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2021년은 미지출을 0으로, 2025년은 빈칸으로 기록했습니다. 기준을 맞추지 않으면 비교가 성립하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>응답 기저 통일</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>교육비 및 사교육비</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로, 2주기는 공란으로 기록하여 응답 기저가 상이하다.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>시계열에서 제외 중</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2025년 빈칸을 0으로 볼지 연구원 확인</t>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2주기 결측을 0으로 처리할지 연구원 확인</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3040,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>선택지 재분류(재코딩)</t>
+          <t>재코딩</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2994,17 +3050,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2021년의 5개 선택지를 2025년의 3개 문항 구조에 맞춰 다시 묶어야 합니다.</t>
+          <t>1주기 5개 선택지를 2주기 3개 문항 구조에 맞추어 재분류해야 한다.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>현재 사용하지 않는 문항</t>
+          <t>현재 미사용 변수</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>교차분석 축으로 쓸지 결정 후 진행</t>
+          <t>교차분석 축 사용 여부 결정 후 진행</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3077,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>발생률로 환산</t>
+          <t>발생률 환산</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3031,17 +3087,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>지금은 '몇 건 일어났나'라는 건수입니다. 학생이 많은 학교는 당연히 건수가 많으므로 학교끼리 비교하려면 학생 수로 나눠야 합니다(예: 학생 1,000명당 건수).</t>
+          <t>현재는 발생 건수이므로 학생 수가 많은 학교일수록 값이 크다. 학교 간 비교를 위해 학생 수 대비 발생률(예: 학생 1,000명당 건수)로 환산해야 한다.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>현재 사용하지 않는 문항. 학교DB에 학년별 학생 수가 있어 계산 가능</t>
+          <t>현재 미사용 변수. 학교DB에 학년별 학생 수가 있어 산출 가능</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>'학교안전' 대분류 도입 여부와 함께 결정</t>
+          <t>'학교안전' 대분류 도입 여부와 연계 결정</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3114,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0~100점 환산</t>
+          <t>환산 100점 부여</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,12 +3124,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>점수 폭이 다른 문항을 한 화면에서 비교하려면 같은 잣대로 바꿔야 합니다.</t>
+          <t>척도 폭이 상이한 문항을 동일 화면에서 비교하기 위해 공통 기준으로 변환해야 한다.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>적용 완료. 모든 지표에 '환산100' 값 제공</t>
+          <t>적용 완료. 전 지표에 환산 100점 값 제공</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3083,37 +3139,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>복합 문항 묶음 5종</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>하위척도 분리</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>학습동기, 학습전략, 자기주도학습, 수업, 교사효능감·사기</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>한 묶음처럼 보이지만 서로 다른 두 가지를 재고 있습니다. 합치면 반대 방향이 상쇄되어 변화가 안 보입니다. 실제로 학습동기를 합치면 27.8→31.5로 완만하지만, 나누면 '시켜서 하는 동기'가 19.1→24.9로 30% 급등한 게 드러납니다.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>단일 묶음으로 보이나 둘 이상의 구인을 측정한다. 합산 시 상반된 방향이 상쇄되어 변화가 은폐된다. 학습동기의 경우 합산 시 27.8→31.5로 완만하나, 분리 시 외재적 동기가 19.1→24.9(+30.4%)로 단독 급등한 것이 확인된다.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>적용 완료</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/docs/변수검수표.xlsx
+++ b/docs/변수검수표.xlsx
@@ -10,10 +10,11 @@
     <sheet name="0. 문서 안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. ID 체계 및 매칭 방법" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. 검토 결과 요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="A. 연계 불가 변수" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B. 추가 검토 변수" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="C. 주의가 필요한 변수" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="D. 처리가 필요한 변수" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3. 적용한 정제 규칙" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="A. 연계 불가 변수" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B. 추가 검토 변수" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="C. 주의가 필요한 변수" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D. 처리가 필요한 변수" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -74,16 +75,24 @@
         <color rgb="00D8DEE8"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00BFC8D6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -451,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,7 +532,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>총 43건. 연계 불가 10건, 추가 검토 12건, 주의 필요 11건, 처리 필요 10건.</t>
+          <t>총 38건. 연계 불가 10건, 추가 검토 12건, 주의 필요 11건, 처리 필요 5건. A~D는 상호 배타적이며 한 변수는 하나의 시트에만 수록한다.</t>
         </is>
       </c>
     </row>
@@ -552,12 +561,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A. 연계 불가 변수</t>
+          <t>3. 적용한 정제 규칙</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>'사용'으로 표시되었으나 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수.</t>
+          <t>개별 변수가 아니라 전체에 일괄 적용한 규칙이다. 모두 정제 스크립트(build.py)가 수행하며 원자료는 수정하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -569,12 +578,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>B. 추가 검토 변수</t>
+          <t>A. 연계 불가 변수</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>'사용' 표시는 없으나 과업지시서 요구사항 충족을 위해 검토가 필요한 변수.</t>
+          <t>'사용'으로 표시되었으나 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수.</t>
         </is>
       </c>
     </row>
@@ -586,12 +595,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C. 주의가 필요한 변수</t>
+          <t>B. 추가 검토 변수</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사용은 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
+          <t>'사용' 표시는 없으나 과업지시서 요구사항 충족을 위해 검토가 필요한 변수.</t>
         </is>
       </c>
     </row>
@@ -603,29 +612,29 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D. 처리가 필요한 변수</t>
+          <t>C. 주의가 필요한 변수</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>역채점·재코딩·결측 보정 등 집계 전 데이터 처리가 필요한 변수.</t>
+          <t>사용은 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>용어 정의</t>
+          <t>시트 구성</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>변수</t>
+          <t>D. 처리가 필요한 변수</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>설문 문항 하나가 데이터에서 하나의 열로 저장되며, 그 열의 이름을 변수명이라 한다. 예: STQ32는 '현재 다니는 학교에 어느 정도 만족하는지'를 묻는 문항이다.</t>
+          <t>'사용' 표시분 중 집계 전 값 자체를 손질해야 하는 변수. 역채점·결측 보정이 해당한다.</t>
         </is>
       </c>
     </row>
@@ -637,12 +646,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1주기 / 2주기</t>
+          <t>변수</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1주기는 2021년 조사, 2주기는 2025년 조사를 가리킨다. 동일 조사를 4년 간격으로 두 차례 실시하였다.</t>
+          <t>설문 문항 하나가 데이터에서 하나의 열로 저장되며, 그 열의 이름을 변수명이라 한다. 예: STQ32는 '현재 다니는 학교에 어느 정도 만족하는지'를 묻는 문항이다.</t>
         </is>
       </c>
     </row>
@@ -654,12 +663,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>결측</t>
+          <t>1주기 / 2주기</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>응답이 비어 있는 상태를 말한다. 무응답, 해당 없음(애초에 묻지 않은 경우), 입력 누락이 모두 빈칸으로 저장되므로 이 셋을 구분하는 것이 검토의 핵심이다.</t>
+          <t>1주기는 2021년 조사, 2주기는 2025년 조사를 가리킨다. 동일 조사를 4년 간격으로 두 차례 실시하였다.</t>
         </is>
       </c>
     </row>
@@ -671,12 +680,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>리커트 척도</t>
+          <t>결측</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>'전혀 그렇지 않다 ~ 매우 그렇다'와 같이 정도를 선택하는 문항 형식이다. 본 조사에는 4점·5점·6점 척도가 혼재한다.</t>
+          <t>응답이 비어 있는 상태를 말한다. 무응답, 해당 없음(애초에 묻지 않은 경우), 입력 누락이 모두 빈칸으로 저장되므로 이 셋을 구분하는 것이 검토의 핵심이다.</t>
         </is>
       </c>
     </row>
@@ -688,12 +697,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>역문항</t>
+          <t>리커트 척도</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>같은 묶음 내 다른 문항과 의미 방향이 반대인 문항이다. 예를 들어 '친구 관계' 묶음에서 다른 문항은 점수가 높을수록 관계가 양호하나, '친구가 나에게 상처를 준 적이 있다'는 점수가 높을수록 부정적이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
+          <t>'전혀 그렇지 않다 ~ 매우 그렇다'와 같이 정도를 선택하는 문항 형식이다. 본 조사에는 4점·5점·6점 척도가 혼재한다.</t>
         </is>
       </c>
     </row>
@@ -705,12 +714,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>역채점 / 역코딩</t>
+          <t>역문항</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>역문항의 점수 방향을 다른 문항과 일치시키는 처리이다. 5점 척도에서는 1↔5, 2↔4로 치환한다.</t>
+          <t>같은 묶음 내 다른 문항과 의미 방향이 반대인 문항이다. 예를 들어 '친구 관계' 묶음에서 다른 문항은 점수가 높을수록 관계가 양호하나, '친구가 나에게 상처를 준 적이 있다'는 점수가 높을수록 부정적이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
         </is>
       </c>
     </row>
@@ -722,12 +731,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>다중응답</t>
+          <t>역채점 / 역코딩</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>'해당하는 항목을 모두 선택' 형식의 문항이다. 선택 항목은 1, 미선택 항목은 0으로 저장되어야 하나, 본 조사에서는 미선택이 결측으로 저장된 사례가 있다.</t>
+          <t>역문항의 점수 방향을 다른 문항과 일치시키는 처리이다. 5점 척도에서는 1↔5, 2↔4로 치환한다.</t>
         </is>
       </c>
     </row>
@@ -739,12 +748,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>조건부 응답</t>
+          <t>다중응답</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>선행 문항의 응답에 따라 응답 대상자가 결정되는 문항이다. 예를 들어 '상담 경험이 있다'고 응답한 대상자에게만 '도움 정도'를 묻는다. 주기별로 응답 대상자 규모가 달라지므로 평균만으로는 비교가 어렵다.</t>
+          <t>'해당하는 항목을 모두 선택' 형식의 문항이다. 선택 항목은 1, 미선택 항목은 0으로 저장되어야 하나, 본 조사에서는 미선택이 결측으로 저장된 사례가 있다.</t>
         </is>
       </c>
     </row>
@@ -756,12 +765,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>응답 기저</t>
+          <t>조건부 응답</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>산출된 수치의 분모, 즉 '몇 명을 대상으로 계산한 값인가'를 뜻한다. 주기 간 기저가 다르면 평균을 직접 비교할 수 없다.</t>
+          <t>선행 문항의 응답에 따라 응답 대상자가 결정되는 문항이다. 예를 들어 '상담 경험이 있다'고 응답한 대상자에게만 '도움 정도'를 묻는다. 주기별로 응답 대상자 규모가 달라지므로 평균만으로는 비교가 어렵다.</t>
         </is>
       </c>
     </row>
@@ -773,12 +782,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>환산 100점</t>
+          <t>응답 기저</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>척도 점수가 상이한 문항을 비교하기 위해 모든 값을 0~100점으로 변환한 값이다. 산식은 (평균 − 척도 최소값) ÷ (척도 최대값 − 척도 최소값) × 100 이다.</t>
+          <t>산출된 수치의 분모, 즉 '몇 명을 대상으로 계산한 값인가'를 뜻한다. 주기 간 기저가 다르면 평균을 직접 비교할 수 없다.</t>
         </is>
       </c>
     </row>
@@ -790,12 +799,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>하위척도</t>
+          <t>환산 100점</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>하나의 문항 묶음이 실제로는 둘 이상의 구인을 측정하는 경우를 말한다. 예를 들어 학습동기 8문항 중 1~4번은 외재적 동기, 5~8번은 내재적 동기를 측정하므로 단일 평균으로 합산해서는 안 된다.</t>
+          <t>척도 점수가 상이한 문항을 비교하기 위해 모든 값을 0~100점으로 변환한 값이다. 산식은 (평균 − 척도 최소값) ÷ (척도 최대값 − 척도 최소값) × 100 이다.</t>
         </is>
       </c>
     </row>
@@ -807,12 +816,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>연계 판정 ①②③④</t>
+          <t>하위척도</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>연구원이 주기 간 문항을 대조하여 부여한 등급이다. ① 연계 가능, ② 조건부 가능, ③ 측정 방식 변경으로 비교 불가, ④ 한 주기에만 존재.</t>
+          <t>하나의 문항 묶음이 실제로는 둘 이상의 구인을 측정하는 경우를 말한다. 예를 들어 학습동기 8문항 중 1~4번은 외재적 동기, 5~8번은 내재적 동기를 측정하므로 단일 평균으로 합산해서는 안 된다.</t>
         </is>
       </c>
     </row>
@@ -824,12 +833,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>지표 ID</t>
+          <t>연계 판정 ①②③④</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>주기 간 변수명이 상이하므로(예: Q28 ↔ STQ32) 문항 단위로 부여한 고정 식별자이다. 예: ST_SAT_TOTAL_01. 3주기 이후에도 동일하게 유지된다.</t>
+          <t>연구원이 주기 간 문항을 대조하여 부여한 등급이다. ① 연계 가능, ② 조건부 가능, ③ 측정 방식 변경으로 비교 불가, ④ 한 주기에만 존재.</t>
         </is>
       </c>
     </row>
@@ -841,10 +850,44 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>지표 ID</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>주기 간 변수명이 상이하므로(예: Q28 ↔ STQ32) 문항 단위로 부여한 고정 식별자이다. 예: ST_SAT_TOTAL_01. 3주기 이후에도 동일하게 유지된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>문항-나머지총점 상관</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>한 문항의 응답과 같은 척도 내 나머지 문항 평균 사이의 상관계수이다. 값이 음수이면 그 문항만 방향이 반대(역문항)임을 뜻하고, 0에 가까우면 척도와 무관하게 움직인다는 뜻이다. 본 검토에서 역문항 판별에 사용하였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>용어 정의</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>시계열</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>동일 항목을 복수 시점에 걸쳐 비교하여 변화를 관찰하는 것으로, 본 대시보드의 핵심 기능이다.</t>
         </is>
@@ -1159,17 +1202,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>6. 유의 사항</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>응답 학교 수의 파일 간 불일치</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>학교DB에는 1주기 179교, 2주기 177교가 등재되어 있으나 실제 응답이 수집된 학교 수는 상이하다. 학생 179→139교, 학부모 179→125교, 교사 179→161교, 학교 설문 179→104교이다. 지역규모로 분할할 경우 읍면지역 표본이 특히 축소되므로 최소 표본 기준 설정이 필요하다.</t>
         </is>
@@ -1186,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1214,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1. ID 체계 및 매칭 방법</t>
+          <t>분류 기준</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1224,67 +1267,101 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>주기 간 식별자 체계의 차이와 두 주기 자료의 연결 방법. 다른 시트를 읽기 전 참조 권장.</t>
+          <t>A~D는 상호 배타적이다. 먼저 변수매칭표의 '사용' 표시 여부로 나누고(표시분 → A·C·D, 미표시분 → B), 표시분은 다시 주기 간 비교 성립 여부(A), 해석상 유의 필요(C), 집계 전 값 처리 필요(D)로 구분한다. 한 변수는 하나의 시트에만 수록한다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A. 연계 불가 변수</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>10</v>
+          <t>1. ID 체계 및 매칭 방법</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>'사용' 표시분 중 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수. 학생 1건, 학부모 7건, 교사 2건.</t>
+          <t>주기 간 식별자 체계의 차이와 두 주기 자료의 연결 방법. 다른 시트를 읽기 전 참조 권장.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>B. 추가 검토 변수</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>12</v>
+          <t>3. 적용한 정제 규칙</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'사용' 미표시분 중 과업지시서 요구사항 충족을 위해 검토가 필요한 변수. 학교용 3건은 '학교안전' 대분류 전체에 해당.</t>
+          <t>개별 변수가 아니라 전체에 일괄 적용한 규칙. 모두 정제 스크립트(build.py)가 수행하며 원자료는 수정하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C. 주의가 필요한 변수</t>
+          <t>A. 연계 불가 변수</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사용 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
+          <t>'사용' 표시분 중 원자료 확인 결과 주기 간 비교가 성립하지 않는 변수. 학생 1건, 학부모 7건, 교사 2건.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>B. 추가 검토 변수</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>'사용' 미표시분 중 과업지시서 요구사항 충족을 위해 검토가 필요한 변수. 학교용 3건은 '학교안전' 대분류 전체에 해당.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C. 주의가 필요한 변수</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>사용 가능하나 수치 해석 및 화면 표기에 유의가 필요한 변수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>D. 처리가 필요한 변수</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>집계 전 데이터 처리가 필요한 변수. 4건 처리 완료, 6건 결정 대기.</t>
+      <c r="B8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>'사용' 표시분 중 집계 전 값 자체를 손질해야 하는 변수. 1건 처리 완료, 4건 결정 대기.</t>
         </is>
       </c>
     </row>
@@ -1294,6 +1371,195 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>R1. 다중응답 결측 보정</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>다중응답 문항에서 미선택이 결측으로 저장된 경우 0으로 치환한다. 적용 대상은 1주기 학부모 Q8_2_1~6이다. 정제 스크립트(build.py)가 자동 처리하며, 마이크로데이터의 '결측보정' 열에 처리 여부가 기록된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>R2. 정의 외 값 결측 처리</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>코드북의 선지 정의 범위를 벗어난 값은 결측으로 처리한다. 단 R1으로 보정한 0은 허용 코드에 포함한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>R3. 연속형 이상값 처리</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>연속형 변수의 음수는 결측 처리하고, 평균과 함께 중앙값·사분위수·상하위 1% 절사평균을 병기한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>R4. 역문항 처리</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>역문항은 자동 역채점하지 않고 지표 정의에 표기만 하며, 하위척도 평균 산출에서 제외한다. 역채점 여부는 연구원 결정 사항이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>R5. 연계 불가 지표 제외</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>연계 판정 ③·④ 및 코딩 이상이 확인된 지표는 시계열 집계에서 제외하고, 주기별 응답 분포는 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>R6. 학교 속성 결합</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>각 응답자의 SCHID로 해당 주기 학교DB를 조회하여 지역규모를 결합한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>환산 100점 부여</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4점·5점·6점 척도가 혼재하므로 모든 선택형 지표에 (평균 − 척도 최소값) ÷ (척도 최대값 − 척도 최소값) × 100 값을 부여한다. 소주제·대분류를 가로지르는 비교의 공통 축으로 사용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>하위척도 분리</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>코드북 문항 라벨에 하위척도가 명시된 5개 묶음(학습동기·학습전략·자기주도학습·수업·교사효능감)을 하위척도 단위로 분리한다. 학습동기의 경우 합산 시 27.8→31.5로 완만하나, 분리 시 외재적 동기가 19.1→24.9(+30.4%)로 단독 급등한 것이 확인된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>적용 주체</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>처리 수행 위치</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>위 규칙은 모두 정제 스크립트 delivery/업체전달_데이터셋_v1/05_재현스크립트/build.py 에서 수행되며, 원자료(.sav)는 수정하지 않는다. 규칙 변경 시 스크립트를 재실행하면 산출물 전체가 재생성된다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1733,42 +1999,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>교사</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>TR_TRAIN_03</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Q27_3 → (해당 없음)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>교사 연수 — 자기계발</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2주기 문항 삭제 (연계 판정 ④)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>대응 문항이 존재하지 않는다. 본 항목 삭제로 인해 후속 항목의 번호가 순차 이동하였으므로, 번호 기준 대응 시 상이한 항목이 연결된다.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>시계열에서 제외. 1주기 단독 값 보유</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>1주기 단독 값의 화면 노출 여부</t>
         </is>
@@ -1779,7 +2045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2242,37 +2508,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>(학교용 설문 전체)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1주기 135개 변수 / 2주기 150개 변수</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>위 2건 외에도 학교 차원의 정보가 다수 포함되어 있다.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>변수매칭이 실시되지 않았다.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>학교 응답은 1주기 179교, 2주기 104교로 표본이 작으며 지역규모 분할 시 더욱 축소된다.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>'학교안전' 우선 검토 후 필요 시 확대</t>
         </is>
@@ -2283,7 +2549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2709,37 +2975,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>응답주체 간 비교 27개 조합</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>다계열 구성 불가</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>동일 주제에 대한 복수 주체 응답을 하나의 화면에 다계열로 제시하는 구조이나, 27개 조합 중 15개는 한쪽 주체 문항이 '사용' 미선택되어 성립하지 않는다.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>업체가 다계열을 전제로 화면을 설계할 경우 빈 계열이 발생한다. 디지털 리터러시 교육, 학생중심수업, 학부모회 활성화가 이에 해당한다.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>산출물에 해당 정보가 포함되어 있지 않음</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>성립 불가 조합 목록을 산출물에 추가</t>
         </is>
@@ -2750,22 +3016,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2781,25 +3049,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>지표 ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>처리 방법</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>문항 내용</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>판별 근거</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>필요한 이유</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>현재 상태</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>결정 사항</t>
         </is>
@@ -2813,32 +3091,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Q15_2 → STQ27_2</t>
+          <t>Q15_6 → STQ27_6</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>ST_RELATION_06</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>역채점</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>학교 친구들이 나에게 상처를 준 적이 있다</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>동일 묶음의 다른 문항은 점수가 높을수록 관계가 양호함을 의미하나 본 문항은 반대이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
+          <t>학교 선생님들은 나에게 무관심하다</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>역채점하지 않고 표기만 함. 하위척도 평균 산출에서 제외</t>
+          <t>문항-나머지총점 상관 r = −0.326(1주기) / −0.135(2주기). 동일 척도 내 다른 문항과 방향이 반대이다.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>역채점 여부 연구원 확인</t>
+          <t>'또래·교사 관계' 척도의 다른 문항은 점수가 높을수록 관계가 양호함을 의미하나 본 문항은 반대이다. 보정 없이 평균을 산출하면 두 방향이 상쇄된다.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>역채점 미적용. 하위척도 평균 산출에서 제외(정제 스크립트 반영)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>역채점 적용 여부 — 연구원 확인</t>
         </is>
       </c>
     </row>
@@ -2850,32 +3138,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Q17_1~5 → STQ29_1~4</t>
+          <t>Q15_2 → STQ27_2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>역코딩</t>
+          <t>ST_RELATION_02</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>차별 경험</t>
+          <t>척도 적합성 검토</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1주기는 1=예 / 2=아니오, 2주기는 1=없다 / 2=있다로 코딩 방향이 반전되어 있다. 보정하지 않으면 결과가 역전된다.</t>
+          <t>학교 친구들이 나에게 상처를 준 적이 있다</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>현재 미사용 변수</t>
+          <t>문항-나머지총점 상관 r = +0.011(1주기) / +0.068(2주기). 0에 근접한다.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>사용 결정 시 역코딩 필수</t>
+          <t>의미상 부정 문항이나 통계적으로는 역방향이 아니라 척도와 무관하게 움직인다. 역채점 대상이 아니며, 척도 평균에 포함할 경우 신뢰도를 저해한다.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>'척도 부적합'으로 표기. 하위척도 평균에서 제외(정제 스크립트 반영)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>단독 지표로 제시할지, 척도에서 완전히 배제할지 — 연구원 확인</t>
         </is>
       </c>
     </row>
@@ -2887,32 +3185,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Q13_2 → PRQ13_2</t>
+          <t>Q13_5 → PRQ13_5</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>PR_RELATION_05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>역채점</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>학교 친구들이 내 아이에게 상처를 준 적이 있다</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>위 학생 문항과 동일한 사유이다.</t>
+          <t>학교 선생님들은 내 아이에게 관심이 부족하다</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>표기만 함. 하위척도 평균에서 제외</t>
+          <t>문항-나머지총점 상관 r = −0.380 / −0.449. 검출된 역문항 중 방향성이 가장 뚜렷하다. 변수매칭표 '필요 처리'란에도 역채점 필요로 명시되어 있다.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>역채점 여부 연구원 확인</t>
+          <t>위와 동일하다. 다만 1주기 '관심이 없다'에서 2주기 '관심이 부족하다'로 표현이 완화되어 응답 분포가 이동했을 가능성이 있다.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>역채점 미적용. 하위척도 평균에서 제외(정제 스크립트 반영)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>역채점 적용 여부 — 연구원 확인</t>
         </is>
       </c>
     </row>
@@ -2924,254 +3232,89 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Q13_5 → PRQ13_5</t>
+          <t>Q13_2 → PRQ13_2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>PR_RELATION_02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>역채점</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>학교 선생님들은 내 아이에게 관심이 부족하다</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>위와 동일하다.</t>
+          <t>학교 친구들이 내 아이에게 상처를 준 적이 있다</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>표기만 함. 하위척도 평균에서 제외</t>
+          <t>문항-나머지총점 상관 r = −0.102 / −0.194. 음의 방향이나 강도는 약하다.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>역채점 여부 연구원 확인</t>
+          <t>위와 동일하다. 동일 문항의 학생 응답(ST_RELATION_02)은 상관이 0에 가까워 주체 간 반응 양상이 다르다.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>역채점 미적용. 하위척도 평균에서 제외(정제 스크립트 반영)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>역채점 적용 여부 — 연구원 확인</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>학부모</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Q8_2_1~6</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Q8_2_1~4 → PRQ3_2_1~4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>PR_TALK_02~05</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>결측 보정 (결측 → 0)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>자녀와의 대화 주제 (다중응답)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>다중응답 문항이나 1주기 자료에 선택(1)만 기록되고 미선택은 결측으로 저장되어 있다. 보정하지 않으면 선택자만 집계되어 선택률이 항상 100%로 산출된다.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>적용 완료(2026-09-07). 이전에는 후속 규칙과 충돌하여 보정이 무효화되고 있었음</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>학부모</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PRQ2_1~5</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>응답 기저 통일</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>교육비 및 사교육비</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1주기는 미지출을 0으로, 2주기는 공란으로 기록하여 응답 기저가 상이하다.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>시계열에서 제외 중</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2주기 결측을 0으로 처리할지 연구원 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>교사</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Q8 → TRQ7 / TRQ9 / TRQ7_1</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>재코딩</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>현재 직위</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1주기 5개 선택지를 2주기 3개 문항 구조에 맞추어 재분류해야 한다.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>현재 미사용 변수</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>교차분석 축 사용 여부 결정 후 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>학교</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Q8_1~8 → SCQ10_1~8</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>발생률 환산</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>학교폭력 및 비행 발생 빈도</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>현재는 발생 건수이므로 학생 수가 많은 학교일수록 값이 크다. 학교 간 비교를 위해 학생 수 대비 발생률(예: 학생 1,000명당 건수)로 환산해야 한다.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>현재 미사용 변수. 학교DB에 학년별 학생 수가 있어 산출 가능</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>'학교안전' 대분류 도입 여부와 연계 결정</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>모든 선택형 문항</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>환산 100점 부여</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4점·5점·6점 척도 혼재</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>척도 폭이 상이한 문항을 동일 화면에서 비교하기 위해 공통 기준으로 변환해야 한다.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>적용 완료. 전 지표에 환산 100점 값 제공</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>복합 문항 묶음 5종</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>하위척도 분리</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>학습동기, 학습전략, 자기주도학습, 수업, 교사효능감·사기</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>단일 묶음으로 보이나 둘 이상의 구인을 측정한다. 합산 시 상반된 방향이 상쇄되어 변화가 은폐된다. 학습동기의 경우 합산 시 27.8→31.5로 완만하나, 분리 시 외재적 동기가 19.1→24.9(+30.4%)로 단독 급등한 것이 확인된다.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>적용 완료</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>완료</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>자녀와의 대화 주제 — 공부·용돈·건강·진로 (다중응답)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>1주기 자료에 0 코드가 존재하지 않고 선택(1)과 결측만 기록되어 있다. 2주기는 0/1이 정상 기록되어 있다.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>다중응답 문항의 미선택이 결측으로 저장되어, 보정 없이 집계하면 선택자만 분모가 되어 선택률이 항상 100%로 산출된다.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>보정 적용됨(정제 스크립트 반영, 2026-09-07). 이전에는 후속 규칙과 충돌하여 보정이 무효화되고 있었음</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>없음 — 처리 완료</t>
         </is>
       </c>
     </row>
